--- a/data/raw/sales/Week 15/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 15/Nexlev/other_channels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 15\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2F8334-49B8-45E6-8CB8-7828D9FEA076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598B503D-1467-45BD-B9BA-4265F5274045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CRED_B2C" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">B2B!$A$1:$Z$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BI Worldwide'!$A$1:$F$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Blinkit Sales'!$A$1:$F$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Blinkit Sales'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'D2C - Nexlev'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -831,7 +831,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -862,38 +862,39 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -934,7 +935,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -959,30 +960,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -1000,7 +977,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1065,19 +1042,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1092,7 +1057,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1104,16 +1069,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8113,7 +8078,7 @@
       <c r="B2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="34" t="s">
         <v>253</v>
       </c>
       <c r="D2" s="13">
@@ -8133,7 +8098,7 @@
       <c r="B3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="34" t="s">
         <v>254</v>
       </c>
       <c r="D3" s="13">
@@ -8187,13 +8152,13 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="34" t="s">
         <v>255</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="34" t="s">
         <v>256</v>
       </c>
       <c r="D6" s="13">
@@ -9717,7 +9682,7 @@
       <c r="B7" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="35" t="s">
         <v>176</v>
       </c>
       <c r="D7" s="16">
@@ -10177,7 +10142,7 @@
       <c r="B30" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="34" t="s">
         <v>142</v>
       </c>
       <c r="D30" s="16">
@@ -10297,7 +10262,7 @@
       <c r="B36" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="34" t="s">
         <v>230</v>
       </c>
       <c r="D36" s="16">
@@ -10357,7 +10322,7 @@
       <c r="B39" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="C39" s="38" t="s">
+      <c r="C39" s="34" t="s">
         <v>231</v>
       </c>
       <c r="D39" s="16">
@@ -10437,7 +10402,7 @@
       <c r="B43" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="38" t="s">
+      <c r="C43" s="34" t="s">
         <v>83</v>
       </c>
       <c r="D43" s="16">
@@ -10497,7 +10462,7 @@
       <c r="B2" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="34" t="s">
         <v>257</v>
       </c>
       <c r="D2" s="21">
@@ -10537,7 +10502,7 @@
       <c r="B4" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="21">
@@ -10617,7 +10582,7 @@
       <c r="B8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="34" t="s">
         <v>256</v>
       </c>
       <c r="D8" s="23">
@@ -11763,1187 +11728,1187 @@
       <c r="W1" s="7"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="25" t="s">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>173</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" t="s">
         <v>174</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" t="s">
         <v>175</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="F2" s="27">
-        <v>3809.32</v>
+      <c r="F2">
+        <v>3809</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="25" t="s">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="C3" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" t="s">
         <v>176</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3">
         <v>11</v>
       </c>
-      <c r="F3" s="27">
-        <v>17702.54</v>
+      <c r="F3">
+        <v>17703</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="25" t="s">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4">
         <v>5</v>
       </c>
-      <c r="F4" s="27">
-        <v>12283.9</v>
+      <c r="F4">
+        <v>12284</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="25" t="s">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="27">
-        <v>2965.25</v>
+      <c r="F5">
+        <v>2965</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="25" t="s">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6">
         <v>9</v>
       </c>
-      <c r="F6" s="27">
-        <v>8890.68</v>
+      <c r="F6">
+        <v>8891</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="25" t="s">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
         <v>177</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" s="27">
-        <v>1693.22</v>
+      <c r="F7">
+        <v>1693</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="25" t="s">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8">
         <v>16</v>
       </c>
-      <c r="F8" s="27">
-        <v>20311.86</v>
+      <c r="F8">
+        <v>20312</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="25" t="s">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" t="s">
         <v>111</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9">
         <v>3</v>
       </c>
-      <c r="F9" s="27">
-        <v>4446.6099999999997</v>
+      <c r="F9">
+        <v>4447</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="25" t="s">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="25" t="s">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="25" t="s">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="25" t="s">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" t="s">
         <v>181</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="F13" s="27">
-        <v>1143.22</v>
+      <c r="F13">
+        <v>1143</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="25" t="s">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14">
         <v>14</v>
       </c>
-      <c r="F14" s="27">
-        <v>25835.59</v>
+      <c r="F14">
+        <v>25836</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="25" t="s">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15">
         <v>2</v>
       </c>
-      <c r="F15" s="27">
-        <v>6015.25</v>
+      <c r="F15">
+        <v>6015</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="25" t="s">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
         <v>182</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" t="s">
         <v>184</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="25" t="s">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17">
         <v>2</v>
       </c>
-      <c r="F17" s="27">
-        <v>4998.3100000000004</v>
+      <c r="F17">
+        <v>4998</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="25" t="s">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" s="25" t="s">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
         <v>185</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" t="s">
         <v>186</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" t="s">
         <v>187</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19">
         <v>3</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19">
         <v>2150</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="25" t="s">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
         <v>188</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" t="s">
         <v>189</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" t="s">
         <v>190</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="25" t="s">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
         <v>191</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" t="s">
         <v>192</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" t="s">
         <v>193</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21">
         <v>2</v>
       </c>
-      <c r="F21" s="27">
-        <v>1947.46</v>
+      <c r="F21">
+        <v>1947</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="25" t="s">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" t="s">
         <v>108</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" t="s">
         <v>109</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="25" t="s">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" t="s">
         <v>115</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23">
         <v>0</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="25" t="s">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
         <v>167</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" t="s">
         <v>168</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" t="s">
         <v>169</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24">
         <v>5</v>
       </c>
-      <c r="F24" s="27">
-        <v>11012.71</v>
+      <c r="F24">
+        <v>11013</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="25" t="s">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
         <v>194</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" t="s">
         <v>195</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" t="s">
         <v>196</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25">
         <v>0</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B26" s="25" t="s">
+      <c r="A26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26">
         <v>2</v>
       </c>
-      <c r="F26" s="27">
-        <v>3557.63</v>
+      <c r="F26">
+        <v>3558</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="25" t="s">
+      <c r="A27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27">
         <v>0</v>
       </c>
-      <c r="F27" s="27">
+      <c r="F27">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="25" t="s">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
         <v>197</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" t="s">
         <v>198</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" t="s">
         <v>199</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28">
         <v>0</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="25" t="s">
+      <c r="A29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="D29" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29">
         <v>2</v>
       </c>
-      <c r="F29" s="27">
-        <v>3330.51</v>
+      <c r="F29">
+        <v>3331</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="25" t="s">
+      <c r="A30" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" t="s">
         <v>201</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" t="s">
         <v>202</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30">
         <v>0</v>
       </c>
-      <c r="F30" s="27">
+      <c r="F30">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B31" s="25" t="s">
+      <c r="A31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" t="s">
         <v>139</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31">
         <v>7</v>
       </c>
-      <c r="F31" s="27">
-        <v>12155.08</v>
+      <c r="F31">
+        <v>12155</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="25" t="s">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" t="s">
         <v>143</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C32" t="s">
         <v>144</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="D32" t="s">
         <v>145</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E32">
         <v>0</v>
       </c>
-      <c r="F32" s="27">
+      <c r="F32">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="25" t="s">
+      <c r="A33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
         <v>146</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="D33" t="s">
         <v>148</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E33">
         <v>0</v>
       </c>
-      <c r="F33" s="27">
+      <c r="F33">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" s="25" t="s">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s">
         <v>203</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" t="s">
         <v>204</v>
       </c>
-      <c r="D34" s="25" t="s">
+      <c r="D34" t="s">
         <v>205</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34">
         <v>4</v>
       </c>
-      <c r="F34" s="27">
-        <v>5416.95</v>
+      <c r="F34">
+        <v>5417</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="25" t="s">
+      <c r="A35" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
         <v>206</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" t="s">
         <v>207</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D35" t="s">
         <v>208</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E35">
         <v>0</v>
       </c>
-      <c r="F35" s="27">
+      <c r="F35">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" s="25" t="s">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="D36" t="s">
         <v>65</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E36">
         <v>9</v>
       </c>
-      <c r="F36" s="27">
-        <v>16263.56</v>
+      <c r="F36">
+        <v>16264</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="25" t="s">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="25" t="s">
+      <c r="C37" t="s">
         <v>210</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="D37" t="s">
         <v>211</v>
       </c>
-      <c r="E37" s="26">
+      <c r="E37">
         <v>4</v>
       </c>
-      <c r="F37" s="27">
-        <v>5335.59</v>
+      <c r="F37">
+        <v>5336</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" s="25" t="s">
+      <c r="A38" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" t="s">
         <v>150</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="D38" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38">
         <v>6</v>
       </c>
-      <c r="F38" s="27">
-        <v>14516.95</v>
+      <c r="F38">
+        <v>14517</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B39" s="25" t="s">
+      <c r="A39" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" t="s">
         <v>212</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" t="s">
         <v>213</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="D39" t="s">
         <v>214</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39" s="27">
+      <c r="F39">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" s="25" t="s">
+      <c r="A40" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" t="s">
         <v>215</v>
       </c>
-      <c r="C40" s="25" t="s">
+      <c r="C40" t="s">
         <v>216</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D40" t="s">
         <v>217</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40">
         <v>0</v>
       </c>
-      <c r="F40" s="27">
+      <c r="F40">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B41" s="25" t="s">
+      <c r="A41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" t="s">
         <v>117</v>
       </c>
-      <c r="D41" s="25" t="s">
+      <c r="D41" t="s">
         <v>118</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41">
         <v>0</v>
       </c>
-      <c r="F41" s="27">
+      <c r="F41">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B42" s="25" t="s">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="25" t="s">
+      <c r="D42" t="s">
         <v>89</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42">
         <v>0</v>
       </c>
-      <c r="F42" s="27">
+      <c r="F42">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="25" t="s">
+      <c r="A43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B43" t="s">
         <v>218</v>
       </c>
-      <c r="C43" s="25" t="s">
+      <c r="C43" t="s">
         <v>219</v>
       </c>
-      <c r="D43" s="25" t="s">
+      <c r="D43" t="s">
         <v>220</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43">
         <v>0</v>
       </c>
-      <c r="F43" s="27">
+      <c r="F43">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B44" s="25" t="s">
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="25" t="s">
+      <c r="C44" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="25" t="s">
+      <c r="D44" t="s">
         <v>97</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44">
         <v>0</v>
       </c>
-      <c r="F44" s="27">
+      <c r="F44">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="25" t="s">
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="25" t="s">
+      <c r="D45" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45">
         <v>1</v>
       </c>
-      <c r="F45" s="27">
-        <v>1185.5899999999999</v>
+      <c r="F45">
+        <v>1186</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B46" s="25" t="s">
+      <c r="A46" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" t="s">
         <v>49</v>
       </c>
-      <c r="D46" s="25" t="s">
+      <c r="D46" t="s">
         <v>50</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46">
         <v>0</v>
       </c>
-      <c r="F46" s="27">
+      <c r="F46">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B47" s="25" t="s">
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C47" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="25" t="s">
+      <c r="D47" t="s">
         <v>133</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47">
         <v>1</v>
       </c>
-      <c r="F47" s="27">
-        <v>846.61</v>
+      <c r="F47">
+        <v>847</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" s="25" t="s">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
         <v>134</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" t="s">
         <v>135</v>
       </c>
-      <c r="D48" s="25" t="s">
+      <c r="D48" t="s">
         <v>136</v>
       </c>
-      <c r="E48" s="26">
+      <c r="E48">
         <v>0</v>
       </c>
-      <c r="F48" s="27">
+      <c r="F48">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" s="25" t="s">
+      <c r="A49" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="25" t="s">
+      <c r="C49" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="25" t="s">
+      <c r="D49" t="s">
         <v>62</v>
       </c>
-      <c r="E49" s="26">
+      <c r="E49">
         <v>0</v>
       </c>
-      <c r="F49" s="27">
+      <c r="F49">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="25" t="s">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
         <v>221</v>
       </c>
-      <c r="C50" s="25" t="s">
+      <c r="C50" t="s">
         <v>222</v>
       </c>
-      <c r="D50" s="25" t="s">
+      <c r="D50" t="s">
         <v>223</v>
       </c>
-      <c r="E50" s="26">
+      <c r="E50">
         <v>0</v>
       </c>
-      <c r="F50" s="27">
+      <c r="F50">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" s="25" t="s">
+      <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
         <v>75</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" t="s">
         <v>76</v>
       </c>
-      <c r="D51" s="25" t="s">
+      <c r="D51" t="s">
         <v>77</v>
       </c>
-      <c r="E51" s="26">
+      <c r="E51">
         <v>0</v>
       </c>
-      <c r="F51" s="27">
+      <c r="F51">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B52" s="25" t="s">
+      <c r="A52" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" t="s">
         <v>156</v>
       </c>
-      <c r="C52" s="25" t="s">
+      <c r="C52" t="s">
         <v>157</v>
       </c>
-      <c r="D52" s="25" t="s">
+      <c r="D52" t="s">
         <v>158</v>
       </c>
-      <c r="E52" s="26">
+      <c r="E52">
         <v>0</v>
       </c>
-      <c r="F52" s="27">
+      <c r="F52">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="25" t="s">
+      <c r="A53" t="s">
+        <v>10</v>
+      </c>
+      <c r="B53" t="s">
         <v>140</v>
       </c>
-      <c r="C53" s="25" t="s">
+      <c r="C53" t="s">
         <v>141</v>
       </c>
-      <c r="D53" s="25" t="s">
+      <c r="D53" t="s">
         <v>142</v>
       </c>
-      <c r="E53" s="26">
+      <c r="E53">
         <v>0</v>
       </c>
-      <c r="F53" s="27">
+      <c r="F53">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="25" t="s">
+      <c r="A54" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" t="s">
         <v>92</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" t="s">
         <v>93</v>
       </c>
-      <c r="D54" s="25" t="s">
+      <c r="D54" t="s">
         <v>41</v>
       </c>
-      <c r="E54" s="26">
+      <c r="E54">
         <v>0</v>
       </c>
-      <c r="F54" s="27">
+      <c r="F54">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B55" s="25" t="s">
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="s">
         <v>224</v>
       </c>
-      <c r="C55" s="25" t="s">
+      <c r="C55" t="s">
         <v>225</v>
       </c>
-      <c r="D55" s="25" t="s">
+      <c r="D55" t="s">
         <v>226</v>
       </c>
-      <c r="E55" s="26">
+      <c r="E55">
         <v>0</v>
       </c>
-      <c r="F55" s="27">
+      <c r="F55">
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56" s="25" t="s">
+      <c r="A56" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="25" t="s">
+      <c r="C56" t="s">
         <v>58</v>
       </c>
-      <c r="D56" s="25" t="s">
+      <c r="D56" t="s">
         <v>59</v>
       </c>
-      <c r="E56" s="26">
+      <c r="E56">
         <v>0</v>
       </c>
-      <c r="F56" s="27">
+      <c r="F56">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B57" s="25" t="s">
+      <c r="A57" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" t="s">
         <v>227</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" t="s">
         <v>228</v>
       </c>
-      <c r="D57" s="25" t="s">
+      <c r="D57" t="s">
         <v>229</v>
       </c>
-      <c r="E57" s="26">
+      <c r="E57">
         <v>0</v>
       </c>
-      <c r="F57" s="27">
+      <c r="F57">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="25" t="s">
+      <c r="A58" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" t="s">
         <v>162</v>
       </c>
-      <c r="C58" s="25" t="s">
+      <c r="C58" t="s">
         <v>163</v>
       </c>
-      <c r="D58" s="25" t="s">
+      <c r="D58" t="s">
         <v>164</v>
       </c>
-      <c r="E58" s="26">
+      <c r="E58">
         <v>4</v>
       </c>
-      <c r="F58" s="27">
-        <v>1452.54</v>
+      <c r="F58">
+        <v>1453</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59" s="25" t="s">
+      <c r="A59" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" t="s">
         <v>152</v>
       </c>
-      <c r="C59" s="25" t="s">
+      <c r="C59" t="s">
         <v>153</v>
       </c>
-      <c r="D59" s="25" t="s">
+      <c r="D59" t="s">
         <v>230</v>
       </c>
-      <c r="E59" s="26">
+      <c r="E59">
         <v>0</v>
       </c>
-      <c r="F59" s="27">
+      <c r="F59">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60" s="25" t="s">
+      <c r="A60" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
         <v>154</v>
       </c>
-      <c r="C60" s="25" t="s">
+      <c r="C60" t="s">
         <v>155</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="D60" t="s">
         <v>231</v>
       </c>
-      <c r="E60" s="26">
+      <c r="E60">
         <v>0</v>
       </c>
-      <c r="F60" s="27">
+      <c r="F60">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F60" xr:uid="{00000000-0001-0000-0700-000000000000}"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0700-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -12983,44 +12948,44 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="24" t="s">
         <v>227</v>
       </c>
-      <c r="B2" s="29" t="str">
+      <c r="B2" s="25" t="str">
         <f>_xlfn.XLOOKUP(C2,[1]Sheet1!$E:$E,[1]Sheet1!$C:$C)</f>
         <v>B0DMT19RWC</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="24">
         <v>1</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="24">
         <v>1637.31</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="25" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="B3" s="29" t="str">
+      <c r="B3" s="25" t="str">
         <f>_xlfn.XLOOKUP(C3,[1]Sheet1!$E:$E,[1]Sheet1!$C:$C)</f>
         <v>B0DVSZ2VVJ</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="24">
         <v>1</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="24">
         <v>5879.51</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="25" t="s">
         <v>10</v>
       </c>
     </row>
@@ -13086,876 +13051,876 @@
       <c r="Z1" s="10"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="D2" s="30">
+      <c r="D2" s="26">
         <v>1</v>
       </c>
-      <c r="E2" s="30">
+      <c r="E2" s="26">
         <v>425</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="31" t="s">
+      <c r="F2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="27" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="26">
         <v>1</v>
       </c>
-      <c r="E3" s="30">
+      <c r="E3" s="26">
         <v>425</v>
       </c>
-      <c r="F3" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="31" t="s">
+      <c r="F3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="27" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="26">
         <v>1</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="26">
         <v>425</v>
       </c>
-      <c r="F4" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="31" t="s">
+      <c r="F4" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="27" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="26">
         <v>1</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="26">
         <v>425</v>
       </c>
-      <c r="F5" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="31" t="s">
+      <c r="F5" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="27" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="26">
         <v>1</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="26">
         <v>509</v>
       </c>
-      <c r="F6" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="31" t="s">
+      <c r="F6" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="27" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="26">
         <v>1</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="26">
         <v>2040</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="31" t="s">
+      <c r="F7" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="27" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <v>1</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="26">
         <v>425</v>
       </c>
-      <c r="F8" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="31" t="s">
+      <c r="F8" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="27" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="26">
         <v>1</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="26">
         <v>425</v>
       </c>
-      <c r="F9" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="31" t="s">
+      <c r="F9" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="27" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="26">
         <v>1</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="26">
         <v>900</v>
       </c>
-      <c r="F10" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="31" t="s">
+      <c r="F10" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="27" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="26">
         <v>1</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="26">
         <v>900</v>
       </c>
-      <c r="F11" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="31" t="s">
+      <c r="F11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="27" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="26">
         <v>1</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="26">
         <v>1700</v>
       </c>
-      <c r="F12" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="31" t="s">
+      <c r="F12" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="26">
         <v>1</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="26">
         <v>850</v>
       </c>
-      <c r="F13" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="31" t="s">
+      <c r="F13" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="26">
         <v>1</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="26">
         <v>1870</v>
       </c>
-      <c r="F14" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="31" t="s">
+      <c r="F14" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="26">
         <v>1</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="26">
         <v>765</v>
       </c>
-      <c r="F15" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="31" t="s">
+      <c r="F15" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="26">
         <v>1</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="26">
         <v>765</v>
       </c>
-      <c r="F16" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="31" t="s">
+      <c r="F16" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="26">
         <v>1</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="26">
         <v>1870</v>
       </c>
-      <c r="F17" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="31" t="s">
+      <c r="F17" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="26">
         <v>1</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="26">
         <v>1700</v>
       </c>
-      <c r="F18" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="31" t="s">
+      <c r="F18" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="26">
         <v>1</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="26">
         <v>850</v>
       </c>
-      <c r="F19" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="31" t="s">
+      <c r="F19" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="26">
         <v>1</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="26">
         <v>680</v>
       </c>
-      <c r="F20" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="31" t="s">
+      <c r="F20" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="26">
         <v>1</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="26">
         <v>1700</v>
       </c>
-      <c r="F21" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="31" t="s">
+      <c r="F21" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="26">
         <v>1</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="26">
         <v>1700</v>
       </c>
-      <c r="F22" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="31" t="s">
+      <c r="F22" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="26">
         <v>1</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="26">
         <v>1700</v>
       </c>
-      <c r="F23" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="31" t="s">
+      <c r="F23" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="26">
         <v>1</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="26">
         <v>5440</v>
       </c>
-      <c r="F24" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="31" t="s">
+      <c r="F24" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="27" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="26">
         <v>1</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="26">
         <v>3499</v>
       </c>
-      <c r="F25" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="31" t="s">
+      <c r="F25" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="27" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="26">
         <v>1</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="26">
         <v>3699</v>
       </c>
-      <c r="F26" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="31" t="s">
+      <c r="F26" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="27" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="26">
         <v>1</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="26">
         <v>3499</v>
       </c>
-      <c r="F27" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="31" t="s">
+      <c r="F27" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="27" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="26">
         <v>1</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="26">
         <v>4499</v>
       </c>
-      <c r="F28" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="31" t="s">
+      <c r="F28" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="27" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="26">
         <v>1</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="26">
         <v>3499</v>
       </c>
-      <c r="F29" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="31" t="s">
+      <c r="F29" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="27" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="26">
         <v>1</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="26">
         <v>8299</v>
       </c>
-      <c r="F30" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="F30" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="26">
         <v>1</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="26">
         <v>2099</v>
       </c>
-      <c r="F31" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="31" t="s">
+      <c r="F31" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="27" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="26">
         <v>2</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="26">
         <v>2984</v>
       </c>
-      <c r="F32" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="31" t="s">
+      <c r="F32" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="27" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="26">
         <v>3</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="26">
         <v>3984</v>
       </c>
-      <c r="F33" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="31" t="s">
+      <c r="F33" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="27" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="26">
         <v>2</v>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="26">
         <v>1932</v>
       </c>
-      <c r="F34" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="31" t="s">
+      <c r="F34" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="27" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="26">
         <v>4</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="26">
         <v>6040</v>
       </c>
-      <c r="F35" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="31" t="s">
+      <c r="F35" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="27" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="26">
         <v>3</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="26">
         <v>4476</v>
       </c>
-      <c r="F36" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="31" t="s">
+      <c r="F36" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="27" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="26">
         <v>5</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="26">
         <v>4070</v>
       </c>
-      <c r="F37" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="31" t="s">
+      <c r="F37" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="27" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="30" t="s">
+      <c r="C38" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="26">
         <v>1</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="26">
         <v>1328</v>
       </c>
-      <c r="F38" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="31" t="s">
+      <c r="F38" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="27" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="26">
         <v>2</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="26">
         <v>1812</v>
       </c>
-      <c r="F39" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="31" t="s">
+      <c r="F39" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="27" t="s">
         <v>244</v>
       </c>
     </row>
@@ -13963,19 +13928,19 @@
       <c r="A40" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="26" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="16">
         <v>8</v>
       </c>
-      <c r="E40" s="35">
+      <c r="E40" s="31">
         <v>11932.16</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" s="29" t="s">
         <v>10</v>
       </c>
       <c r="G40" s="18" t="s">
@@ -13986,19 +13951,19 @@
       <c r="A41" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="B41" s="31" t="s">
+      <c r="B41" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="30" t="s">
+      <c r="C41" s="26" t="s">
         <v>94</v>
       </c>
       <c r="D41" s="16">
         <v>4</v>
       </c>
-      <c r="E41" s="35">
+      <c r="E41" s="31">
         <v>4067.8</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="29" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="18" t="s">
@@ -14009,19 +13974,19 @@
       <c r="A42" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B42" s="31" t="s">
+      <c r="B42" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" s="30" t="s">
         <v>100</v>
       </c>
       <c r="D42" s="16">
         <v>10</v>
       </c>
-      <c r="E42" s="35">
+      <c r="E42" s="31">
         <v>7619</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="F42" s="29" t="s">
         <v>10</v>
       </c>
       <c r="G42" s="18" t="s">
@@ -14032,19 +13997,19 @@
       <c r="A43" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="27" t="s">
         <v>210</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="C43" s="26" t="s">
         <v>211</v>
       </c>
       <c r="D43" s="16">
         <v>6</v>
       </c>
-      <c r="E43" s="35">
+      <c r="E43" s="31">
         <v>8135.58</v>
       </c>
-      <c r="F43" s="33" t="s">
+      <c r="F43" s="29" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="18" t="s">
@@ -14055,19 +14020,19 @@
       <c r="A44" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="31" t="s">
+      <c r="B44" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C44" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D44" s="16">
         <v>8</v>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="31">
         <v>14101.68</v>
       </c>
-      <c r="F44" s="33" t="s">
+      <c r="F44" s="29" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="18" t="s">
@@ -14078,19 +14043,19 @@
       <c r="A45" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="31" t="s">
+      <c r="B45" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="26">
         <v>15</v>
       </c>
-      <c r="E45" s="30">
+      <c r="E45" s="26">
         <v>26440.65</v>
       </c>
-      <c r="F45" s="33" t="s">
+      <c r="F45" s="29" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="18" t="s">
@@ -14098,25 +14063,25 @@
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B46" s="30" t="s">
+      <c r="B46" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="C46" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="D46" s="36">
+      <c r="D46" s="32">
         <v>30</v>
       </c>
-      <c r="E46" s="35">
+      <c r="E46" s="31">
         <v>69737.399999999994</v>
       </c>
-      <c r="F46" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="30" t="s">
+      <c r="F46" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="26" t="s">
         <v>252</v>
       </c>
     </row>

--- a/data/raw/sales/Week 15/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 15/Nexlev/other_channels.xlsx
@@ -7454,7 +7454,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="34" t="inlineStr">
         <is>
-          <t>FBA79347</t>
+          <t>FBK79347</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -10430,7 +10430,7 @@
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>FBA79598</t>
+          <t>FBK79598</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
